--- a/DateBase/orders/Nha Thu_2026-4-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-4.xlsx
@@ -523,6 +523,9 @@
       <c r="C11" t="str">
         <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -581,7 +584,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05510151010101060</v>
+        <v>05510151010101065</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-4-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,12 +524,92 @@
         <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F11" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>4</v>
+      </c>
+      <c r="C12" t="str">
+        <v>462_五针松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -584,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05510151010101065</v>
+        <v>0551015101010106810925551510100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-4-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-4.xlsx
@@ -606,6 +606,12 @@
       <c r="A21" t="str">
         <v>5</v>
       </c>
+      <c r="C21" t="str">
+        <v>327_文竹_asparagus fern_undefined_1bunch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -664,7 +670,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0551015101010106810925551510100</v>
+        <v>05510151010101068109255515101015</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-4-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -613,9 +613,79 @@
         <v>15</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>6</v>
+      </c>
+      <c r="C28" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -670,7 +740,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05510151010101068109255515101015</v>
+        <v>055101510101010681092555151010151053010302015030</v>
       </c>
     </row>
   </sheetData>
